--- a/AAII_Financials/Yearly/LEN.B_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/LEN.B_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="92">
   <si>
     <t>LEN.B</t>
   </si>
@@ -1682,16 +1682,16 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>6398700</v>
+        <v>15100</v>
       </c>
       <c r="E42" s="3">
-        <v>3658000</v>
+        <v>32600</v>
       </c>
       <c r="F42" s="3">
-        <v>2002200</v>
+        <v>0</v>
       </c>
       <c r="G42" s="3">
-        <v>1733700</v>
+        <v>0</v>
       </c>
       <c r="H42" s="3">
         <v>0</v>
@@ -1780,17 +1780,17 @@
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E45" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F45" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G45" s="3" t="s">
-        <v>8</v>
+      <c r="D45" s="3">
+        <v>6383600</v>
+      </c>
+      <c r="E45" s="3">
+        <v>3625400</v>
+      </c>
+      <c r="F45" s="3">
+        <v>2002200</v>
+      </c>
+      <c r="G45" s="3">
+        <v>1733700</v>
       </c>
       <c r="H45" s="3" t="s">
         <v>8</v>
